--- a/data/trans_bre/IP2002-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/IP2002-Provincia-trans_bre.xlsx
@@ -602,7 +602,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -660,49 +660,49 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-9,02; 10,37</t>
+          <t>-9,91; 9,26</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-20,09; -0,0</t>
+          <t>-19,04; 0,57</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,35; 14,37</t>
+          <t>-3,98; 12,84</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-8,91; 9,12</t>
+          <t>-8,51; 9,56</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-64,02; 194,28</t>
+          <t>-73,2; 189,83</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-87,41; 11,77</t>
+          <t>-85,94; 22,08</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-44,66; 559,78</t>
+          <t>-51,42; 415,79</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-75,93; 275,69</t>
+          <t>-76,03; 282,2</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -760,49 +760,49 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-4,09; 7,91</t>
+          <t>-5,21; 7,67</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-6,82; 3,46</t>
+          <t>-6,99; 3,6</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-9,02; 1,27</t>
+          <t>-9,09; 1,14</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-5,73; 5,48</t>
+          <t>-5,48; 5,53</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-40,63; 148,92</t>
+          <t>-48,6; 143,66</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-79,03; 145,13</t>
+          <t>-79,69; 137,97</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-89,06; 63,62</t>
+          <t>-90,74; 57,28</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-79,24; 267,5</t>
+          <t>-78,89; 254,72</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -860,22 +860,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,42; 9,5</t>
+          <t>-1,38; 9,15</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,23; 6,86</t>
+          <t>-4,99; 6,66</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,03; 4,29</t>
+          <t>-2,03; 5,18</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-5,02; 12,63</t>
+          <t>-4,28; 12,67</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -885,17 +885,17 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
+          <t>-100,0; 517,91</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-53,95; 299,39</t>
+          <t>-43,11; 355,32</t>
         </is>
       </c>
     </row>
@@ -960,22 +960,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,14; 12,42</t>
+          <t>0,84; 11,45</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,82; 10,23</t>
+          <t>-2,46; 10,44</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-4,04; 14,5</t>
+          <t>-4,28; 13,94</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-1,43; 5,6</t>
+          <t>-1,36; 5,46</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -985,12 +985,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-45,85; 562,91</t>
+          <t>-44,27; 516,84</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-31,33; 243,44</t>
+          <t>-35,95; 220,85</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1060,32 +1060,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-14,55; 6,93</t>
+          <t>-14,23; 7,93</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-11,91; 11,06</t>
+          <t>-11,27; 9,98</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-9,08; 3,09</t>
+          <t>-8,85; 1,87</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,15; 13,04</t>
+          <t>-6,17; 12,89</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-82,29; 169,83</t>
+          <t>-82,21; 155,94</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-75,12; 211,17</t>
+          <t>-72,6; 208,77</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1095,14 +1095,14 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-57,82; 429,44</t>
+          <t>-66,86; 512,59</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1160,37 +1160,37 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-12,6; 1,87</t>
+          <t>-12,4; 1,82</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-15,59; 2,61</t>
+          <t>-16,58; 2,94</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-1,94; 18,03</t>
+          <t>-2,33; 18,11</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-4,46; 8,31</t>
+          <t>-4,39; 8,99</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-92,99; 91,95</t>
+          <t>-92,09; 76,91</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-88,76; 56,37</t>
+          <t>-88,65; 85,5</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-36,2; 846,68</t>
+          <t>-39,32; 991,77</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-7,51; 1,81</t>
+          <t>-7,57; 2,06</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-5,03; 4,99</t>
+          <t>-5,13; 4,72</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,88; 6,11</t>
+          <t>-0,82; 6,2</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-4,93; 6,78</t>
+          <t>-5,69; 7,27</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-79,14; 55,39</t>
+          <t>-78,44; 66,51</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-65,03; 199,11</t>
+          <t>-66,08; 176,97</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-48,88; 1261,99</t>
+          <t>-56,97; 988,18</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-42,23; 130,46</t>
+          <t>-46,63; 145,6</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-5,83; 4,61</t>
+          <t>-5,89; 5,3</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-4,55; 2,79</t>
+          <t>-4,55; 2,72</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-3,18; 4,93</t>
+          <t>-3,11; 5,02</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-2,24; 3,33</t>
+          <t>-2,29; 3,56</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-48,48; 65,65</t>
+          <t>-48,66; 81,87</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-68,54; 96,22</t>
+          <t>-67,37; 99,38</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-50,77; 190,59</t>
+          <t>-52,05; 213,35</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-2,56; 2,17</t>
+          <t>-2,69; 2,01</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,73; 0,86</t>
+          <t>-3,83; 0,73</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 3,61</t>
+          <t>-0,6; 3,49</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,59; 3,05</t>
+          <t>-1,25; 3,24</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-30,84; 36,18</t>
+          <t>-32,34; 32,61</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-45,24; 15,49</t>
+          <t>-46,34; 13,19</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-12,57; 94,65</t>
+          <t>-10,23; 87,79</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-25,29; 71,79</t>
+          <t>-21,13; 84,68</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP2002-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/IP2002-Provincia-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-9,91; 9,26</t>
+          <t>-9,01; 10,9</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-19,04; 0,57</t>
+          <t>-19,47; -0,5</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,98; 12,84</t>
+          <t>-3,67; 14,34</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-8,51; 9,56</t>
+          <t>-8,72; 8,69</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-73,2; 189,83</t>
+          <t>-69,51; 263,3</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-85,94; 22,08</t>
+          <t>-87,87; 7,24</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-51,42; 415,79</t>
+          <t>-46,37; 547,16</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-76,03; 282,2</t>
+          <t>-75,12; 213,88</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-5,21; 7,67</t>
+          <t>-4,17; 9,13</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-6,99; 3,6</t>
+          <t>-7,32; 3,64</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-9,09; 1,14</t>
+          <t>-9,23; 0,61</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-5,48; 5,53</t>
+          <t>-5,96; 5,31</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-48,6; 143,66</t>
+          <t>-42,73; 186,87</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-79,69; 137,97</t>
+          <t>-82,01; 146,55</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-90,74; 57,28</t>
+          <t>-90,53; 34,46</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-78,89; 254,72</t>
+          <t>-83,9; 240,34</t>
         </is>
       </c>
     </row>
@@ -860,22 +860,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,38; 9,15</t>
+          <t>-1,48; 9,43</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,99; 6,66</t>
+          <t>-4,98; 6,44</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,03; 5,18</t>
+          <t>-2,04; 5,1</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,28; 12,67</t>
+          <t>-5,01; 12,85</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 517,91</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-43,11; 355,32</t>
+          <t>-48,28; 353,94</t>
         </is>
       </c>
     </row>
@@ -960,22 +960,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,84; 11,45</t>
+          <t>0,89; 11,63</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,46; 10,44</t>
+          <t>-3,08; 9,57</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-4,28; 13,94</t>
+          <t>-3,38; 14,67</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-1,36; 5,46</t>
+          <t>-1,51; 5,37</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -985,12 +985,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-44,27; 516,84</t>
+          <t>-51,48; 493,41</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-35,95; 220,85</t>
+          <t>-31,64; 263,68</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1060,32 +1060,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-14,23; 7,93</t>
+          <t>-16,19; 6,19</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-11,27; 9,98</t>
+          <t>-11,87; 10,74</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-8,85; 1,87</t>
+          <t>-9,03; 2,11</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-6,17; 12,89</t>
+          <t>-5,73; 13,3</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-82,21; 155,94</t>
+          <t>-86,33; 102,98</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-72,6; 208,77</t>
+          <t>-75,15; 204,95</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-66,86; 512,59</t>
+          <t>-57,08; 477,95</t>
         </is>
       </c>
     </row>
@@ -1160,37 +1160,37 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-12,4; 1,82</t>
+          <t>-13,49; 1,66</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-16,58; 2,94</t>
+          <t>-18,01; 2,07</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-2,33; 18,11</t>
+          <t>-1,63; 17,37</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-4,39; 8,99</t>
+          <t>-4,41; 8,86</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-92,09; 76,91</t>
+          <t>-100,0; 68,47</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-88,65; 85,5</t>
+          <t>-90,75; 57,4</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-39,32; 991,77</t>
+          <t>-29,72; 925,63</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-7,57; 2,06</t>
+          <t>-7,76; 1,43</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-5,13; 4,72</t>
+          <t>-5,75; 4,47</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,82; 6,2</t>
+          <t>-1,18; 5,9</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-5,69; 7,27</t>
+          <t>-4,5; 7,89</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-78,44; 66,51</t>
+          <t>-80,56; 39,24</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-66,08; 176,97</t>
+          <t>-69,24; 163,61</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-56,97; 988,18</t>
+          <t>-70,39; 935,45</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-46,63; 145,6</t>
+          <t>-44,59; 149,97</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-5,89; 5,3</t>
+          <t>-5,9; 5,08</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-4,55; 2,72</t>
+          <t>-4,64; 2,52</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-3,11; 5,02</t>
+          <t>-2,85; 5,48</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-2,29; 3,56</t>
+          <t>-2,35; 3,11</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-48,66; 81,87</t>
+          <t>-48,89; 71,94</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-67,37; 99,38</t>
+          <t>-65,72; 100,35</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-52,05; 213,35</t>
+          <t>-49,68; 206,7</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-2,69; 2,01</t>
+          <t>-2,35; 2,21</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,83; 0,73</t>
+          <t>-3,52; 0,83</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,6; 3,49</t>
+          <t>-0,75; 3,43</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,25; 3,24</t>
+          <t>-1,33; 2,95</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-32,34; 32,61</t>
+          <t>-28,22; 37,15</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-46,34; 13,19</t>
+          <t>-43,91; 14,26</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-10,23; 87,79</t>
+          <t>-14,0; 85,88</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-21,13; 84,68</t>
+          <t>-21,94; 72,81</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP2002-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/IP2002-Provincia-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-0,49</t>
+          <t>-1,92</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-6,01%</t>
+          <t>-21,66%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-9,01; 10,9</t>
+          <t>-9,02; 10,37</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-19,47; -0,5</t>
+          <t>-20,09; -0,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,67; 14,34</t>
+          <t>-3,35; 14,37</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-8,72; 8,69</t>
+          <t>-11,31; 6,16</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-69,51; 263,3</t>
+          <t>-64,02; 194,28</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-87,87; 7,24</t>
+          <t>-87,41; 11,77</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-46,37; 547,16</t>
+          <t>-44,66; 559,78</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-75,12; 213,88</t>
+          <t>-78,98; 169,87</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0,18</t>
+          <t>1,84</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>43,57%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-4,17; 9,13</t>
+          <t>-4,09; 7,91</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-7,32; 3,64</t>
+          <t>-6,82; 3,46</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-9,23; 0,61</t>
+          <t>-9,02; 1,27</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-5,96; 5,31</t>
+          <t>-3,81; 8,08</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-42,73; 186,87</t>
+          <t>-40,63; 148,92</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-82,01; 146,55</t>
+          <t>-79,03; 145,13</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-90,53; 34,46</t>
+          <t>-89,06; 63,62</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-83,9; 240,34</t>
+          <t>-67,38; 420,06</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4,07</t>
+          <t>4,52</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>52,91%</t>
+          <t>62,18%</t>
         </is>
       </c>
     </row>
@@ -860,22 +860,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,48; 9,43</t>
+          <t>-1,42; 9,5</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,98; 6,44</t>
+          <t>-5,23; 6,86</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,04; 5,1</t>
+          <t>-2,03; 4,29</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-5,01; 12,85</t>
+          <t>-4,13; 13,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-48,28; 353,94</t>
+          <t>-51,15; 335,05</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0,65</t>
+          <t>0,7</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>92,06%</t>
+          <t>108,09%</t>
         </is>
       </c>
     </row>
@@ -960,22 +960,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,89; 11,63</t>
+          <t>1,14; 12,42</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-3,08; 9,57</t>
+          <t>-2,82; 10,23</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-3,38; 14,67</t>
+          <t>-4,04; 14,5</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-1,51; 5,37</t>
+          <t>-1,3; 5,92</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -985,12 +985,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-51,48; 493,41</t>
+          <t>-45,85; 562,91</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-31,64; 263,68</t>
+          <t>-31,33; 243,44</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3,58</t>
+          <t>3,44</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>51,71%</t>
+          <t>46,58%</t>
         </is>
       </c>
     </row>
@@ -1060,32 +1060,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-16,19; 6,19</t>
+          <t>-14,55; 6,93</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-11,87; 10,74</t>
+          <t>-11,91; 11,06</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-9,03; 2,11</t>
+          <t>-9,08; 3,09</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,73; 13,3</t>
+          <t>-5,26; 13,27</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-86,33; 102,98</t>
+          <t>-82,29; 169,83</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-75,15; 204,95</t>
+          <t>-75,12; 211,17</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-57,08; 477,95</t>
+          <t>-58,46; 454,06</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1,38</t>
+          <t>1,89</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>41,63%</t>
+          <t>64,57%</t>
         </is>
       </c>
     </row>
@@ -1160,37 +1160,37 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-13,49; 1,66</t>
+          <t>-12,6; 1,87</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-18,01; 2,07</t>
+          <t>-15,59; 2,61</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-1,63; 17,37</t>
+          <t>-1,94; 18,03</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-4,41; 8,86</t>
+          <t>-3,58; 9,29</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 68,47</t>
+          <t>-92,99; 91,95</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-90,75; 57,4</t>
+          <t>-88,76; 56,37</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-29,72; 925,63</t>
+          <t>-36,2; 846,68</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1,14</t>
+          <t>1,17</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>13,01%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-7,76; 1,43</t>
+          <t>-7,51; 1,81</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-5,75; 4,47</t>
+          <t>-5,03; 4,99</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,18; 5,9</t>
+          <t>-0,88; 6,11</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-4,5; 7,89</t>
+          <t>-4,96; 7,3</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-80,56; 39,24</t>
+          <t>-79,14; 55,39</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-69,24; 163,61</t>
+          <t>-65,03; 199,11</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-70,39; 935,45</t>
+          <t>-48,88; 1261,99</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-44,59; 149,97</t>
+          <t>-42,59; 129,07</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0,25</t>
+          <t>0,38</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>15,54%</t>
+          <t>24,98%</t>
         </is>
       </c>
     </row>
@@ -1360,37 +1360,37 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-5,9; 5,08</t>
+          <t>-5,83; 4,61</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-4,64; 2,52</t>
+          <t>-4,55; 2,79</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-2,85; 5,48</t>
+          <t>-3,18; 4,93</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-2,35; 3,11</t>
+          <t>-2,02; 3,56</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-48,89; 71,94</t>
+          <t>-48,48; 65,65</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-65,72; 100,35</t>
+          <t>-68,54; 96,22</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-49,68; 206,7</t>
+          <t>-50,77; 190,59</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -1427,7 +1427,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>0,9</t>
+          <t>1,19</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>17,97%</t>
+          <t>23,92%</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-2,35; 2,21</t>
+          <t>-2,56; 2,17</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,52; 0,83</t>
+          <t>-3,73; 0,86</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 3,43</t>
+          <t>-0,67; 3,61</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,33; 2,95</t>
+          <t>-1,29; 3,28</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-28,22; 37,15</t>
+          <t>-30,84; 36,18</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-43,91; 14,26</t>
+          <t>-45,24; 15,49</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-14,0; 85,88</t>
+          <t>-12,57; 94,65</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-21,94; 72,81</t>
+          <t>-20,55; 81,38</t>
         </is>
       </c>
     </row>
